--- a/questions (1).xlsx
+++ b/questions (1).xlsx
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R48"/>
+  <dimension ref="A1:R49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4132,6 +4132,76 @@
         </is>
       </c>
     </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>q_f16586bc</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>yo yo</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>ass</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>ss</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>dd</t>
+        </is>
+      </c>
+      <c r="H49" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O49" s="9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P49" s="9" t="inlineStr"/>
+      <c r="Q49" s="9" t="inlineStr"/>
+      <c r="R49" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4326,7 +4396,7 @@
       </c>
       <c r="B2" s="18" t="inlineStr">
         <is>
-          <t>World Cup Quiz Pack</t>
+          <t>No Pack Loaded</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4408,7 @@
       </c>
       <c r="B3" s="20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4420,7 @@
       </c>
       <c r="B4" s="18" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4432,7 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4444,7 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
     </row>

--- a/questions (1).xlsx
+++ b/questions (1).xlsx
@@ -4191,10 +4191,14 @@
       </c>
       <c r="O49" s="9" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P49" s="9" t="inlineStr"/>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="P49" s="9" t="inlineStr">
+        <is>
+          <t>media/12471037-uhd_3840_2160_24fps_2.mp4</t>
+        </is>
+      </c>
       <c r="Q49" s="9" t="inlineStr"/>
       <c r="R49" s="13" t="inlineStr">
         <is>

--- a/questions (1).xlsx
+++ b/questions (1).xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet name="Questions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="📖 Instructions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Config" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -124,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -167,13 +166,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -689,7 +681,7 @@
         </is>
       </c>
       <c r="H2" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -697,13 +689,13 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>0</v>
@@ -713,15 +705,15 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>world_cup</t>
-        </is>
-      </c>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>media/12471037-uhd_3840_2160_24fps_3.mp4</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr"/>
       <c r="R2" s="7" t="inlineStr">
         <is>
           <t>YES</t>
@@ -4365,130 +4357,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="16" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="B1" s="16" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B2" s="18" t="inlineStr">
-        <is>
-          <t>No Pack Loaded</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>rounds</t>
-        </is>
-      </c>
-      <c r="B3" s="20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>questions_per_round</t>
-        </is>
-      </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>timer_seconds</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>answer_seconds</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>shuffle_questions</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>enable_cascading_attempts</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>penalty_for_wrong</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>